--- a/LOV3_HTX_Adjusted_EBITDA_Addback_Schedule.xlsx
+++ b/LOV3_HTX_Adjusted_EBITDA_Addback_Schedule.xlsx
@@ -713,10 +713,10 @@
         <v>3732</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2489.75</v>
+        <v>7989.75</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>6221.75</v>
+        <v>11721.75</v>
       </c>
     </row>
     <row r="16">
@@ -745,10 +745,10 @@
         <v>75540.70999999999</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>104841.4</v>
+        <v>110341.4</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>180382.11</v>
+        <v>185882.11</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -768,10 +768,10 @@
         <v>464152.9</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>371618.64</v>
+        <v>377118.64</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>835771.54</v>
+        <v>841271.54</v>
       </c>
     </row>
     <row r="20">
@@ -784,10 +784,10 @@
         <v>0.2611363654188097</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.1940709159823029</v>
+        <v>0.1969431885838674</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.2263555720197512</v>
+        <v>0.2278451604856478</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -807,10 +807,10 @@
         <v>9773.33</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>46415.23</v>
+        <v>40915.23</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>56188.56</v>
+        <v>50688.56</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
